--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -213,7 +213,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:04:29.777Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:27:15.652Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1791,30 +1791,33 @@
     <t>A cart expires 20 minutes after it is created and never creates a reservation itself.</t>
   </si>
   <si>
+    <t>agreed</t>
+  </si>
+  <si>
+    <t>BR-122</t>
+  </si>
+  <si>
+    <t>Cart expiry and no implicit reservation</t>
+  </si>
+  <si>
+    <t>minutes=20</t>
+  </si>
+  <si>
+    <t>enhanced</t>
+  </si>
+  <si>
+    <t>A cart expires 30 minutes after it is created and never creates a reservation itself.</t>
+  </si>
+  <si>
+    <t>REQ-123</t>
+  </si>
+  <si>
+    <t>A price change of more than 1% must be acknowledged by the guest before checkout.</t>
+  </si>
+  <si>
     <t>code-only</t>
   </si>
   <si>
-    <t>BR-122</t>
-  </si>
-  <si>
-    <t>Cart expiry and no implicit reservation</t>
-  </si>
-  <si>
-    <t>minutes=20</t>
-  </si>
-  <si>
-    <t>enhanced</t>
-  </si>
-  <si>
-    <t>A cart expires 30 minutes after it is created and never creates a reservation itself.</t>
-  </si>
-  <si>
-    <t>REQ-123</t>
-  </si>
-  <si>
-    <t>A price change of more than 1% must be acknowledged by the guest before checkout.</t>
-  </si>
-  <si>
     <t>BR-123</t>
   </si>
   <si>
@@ -1954,9 +1957,6 @@
   </si>
   <si>
     <t>A confirmed reservation on a refundable rate can be cancelled free of charge up to 48 hours before check-in; a later cancellation is refused and the reservation stays confirmed.</t>
-  </si>
-  <si>
-    <t>agreed</t>
   </si>
   <si>
     <t>BR-131</t>
@@ -5566,7 +5566,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:04:31.512Z</t>
+    <t>2026-10-05T16:27:17.630Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5578,7 +5578,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-05T16:04:31.556Z</t>
+    <t>2026-10-05T16:27:17.672Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1532</v>
@@ -6535,7 +6535,7 @@
         <v>1533</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1537</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1536</v>
@@ -6573,7 +6573,7 @@
         <v>1533</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>1539</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1536</v>
@@ -6611,7 +6611,7 @@
         <v>1533</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>1541</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>1536</v>
@@ -6649,7 +6649,7 @@
         <v>1533</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>1542</v>
@@ -12608,7 +12608,7 @@
         <v>578</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>1262</v>
@@ -12649,7 +12649,7 @@
         <v>578</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>1269</v>
@@ -12681,16 +12681,16 @@
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>1275</v>
@@ -12725,13 +12725,13 @@
         <v>399</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>1282</v>
@@ -12766,13 +12766,13 @@
         <v>399</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>1288</v>
@@ -12807,13 +12807,13 @@
         <v>399</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>1292</v>
@@ -12845,16 +12845,16 @@
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>1297</v>
@@ -12886,16 +12886,16 @@
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C125" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>1305</v>
@@ -12927,16 +12927,16 @@
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C126" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>1311</v>
@@ -12968,16 +12968,16 @@
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>1317</v>
@@ -13012,13 +13012,13 @@
         <v>145</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1323</v>
@@ -13053,13 +13053,13 @@
         <v>145</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>1329</v>
@@ -13094,13 +13094,13 @@
         <v>145</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1335</v>
@@ -13135,13 +13135,13 @@
         <v>145</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>1341</v>
@@ -13176,13 +13176,13 @@
         <v>145</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1347</v>
@@ -13217,13 +13217,13 @@
         <v>145</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>1353</v>
@@ -13255,16 +13255,16 @@
     </row>
     <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="C134" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1359</v>
@@ -13294,16 +13294,16 @@
     </row>
     <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1364</v>
@@ -13333,13 +13333,13 @@
     </row>
     <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="C136" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>627</v>
@@ -13374,13 +13374,13 @@
     </row>
     <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="C137" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>627</v>
@@ -13415,7 +13415,7 @@
     </row>
     <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>630</v>
@@ -13456,7 +13456,7 @@
     </row>
     <row r="139" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>634</v>
@@ -18754,16 +18754,16 @@
         <v>60</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>65</v>
@@ -18778,13 +18778,13 @@
     </row>
     <row r="125" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>60</v>
@@ -18793,13 +18793,13 @@
         <v>571</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>65</v>
@@ -18811,33 +18811,33 @@
         <v>2</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="126" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>399</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>65</v>
@@ -18852,13 +18852,13 @@
     </row>
     <row r="127" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>60</v>
@@ -18867,13 +18867,13 @@
         <v>571</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>65</v>
@@ -18885,33 +18885,33 @@
         <v>2</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>65</v>
@@ -18926,28 +18926,28 @@
     </row>
     <row r="129" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>65</v>
@@ -18962,13 +18962,13 @@
     </row>
     <row r="130" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>60</v>
@@ -18977,19 +18977,19 @@
         <v>61</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K130" s="2">
         <v>1</v>
@@ -18998,13 +18998,13 @@
     </row>
     <row r="131" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>60</v>
@@ -19013,19 +19013,19 @@
         <v>61</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K131" s="2">
         <v>1</v>
@@ -19034,19 +19034,19 @@
     </row>
     <row r="132" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>627</v>
@@ -19061,7 +19061,7 @@
         <v>65</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K132" s="2">
         <v>1</v>
@@ -19073,7 +19073,7 @@
         <v>630</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>631</v>
@@ -19082,7 +19082,7 @@
         <v>60</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>632</v>
@@ -19097,7 +19097,7 @@
         <v>65</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K133" s="2">
         <v>1</v>
@@ -19109,7 +19109,7 @@
         <v>634</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>635</v>
@@ -19133,7 +19133,7 @@
         <v>65</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K134" s="2">
         <v>1</v>
@@ -19154,7 +19154,7 @@
         <v>60</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>640</v>
@@ -19169,7 +19169,7 @@
         <v>65</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K135" s="2">
         <v>1</v>
@@ -19190,7 +19190,7 @@
         <v>60</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>644</v>
@@ -19205,7 +19205,7 @@
         <v>65</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K136" s="2">
         <v>1</v>
@@ -19226,7 +19226,7 @@
         <v>60</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>650</v>
@@ -19241,7 +19241,7 @@
         <v>65</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K137" s="2">
         <v>1</v>
@@ -19262,7 +19262,7 @@
         <v>60</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>626</v>
+        <v>571</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>654</v>
@@ -19277,7 +19277,7 @@
         <v>65</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K138" s="2">
         <v>1</v>
@@ -19313,7 +19313,7 @@
         <v>95</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K139" s="2">
         <v>1</v>
@@ -25618,7 +25618,7 @@
         <v>692</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>693</v>
@@ -25665,7 +25665,7 @@
         <v>692</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>693</v>
@@ -26217,7 +26217,7 @@
         <v>1430</v>
       </c>
       <c r="E2" s="2">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -26335,7 +26335,7 @@
         <v>1430</v>
       </c>
       <c r="E8" s="2">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -26353,7 +26353,7 @@
         <v>1430</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -26371,7 +26371,7 @@
         <v>1430</v>
       </c>
       <c r="E10" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -26425,7 +26425,7 @@
         <v>1430</v>
       </c>
       <c r="E13" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -26503,7 +26503,7 @@
         <v>1430</v>
       </c>
       <c r="E17" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -26521,7 +26521,7 @@
         <v>1430</v>
       </c>
       <c r="E18" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -26579,7 +26579,7 @@
         <v>1430</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -26617,7 +26617,7 @@
         <v>1430</v>
       </c>
       <c r="E23" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -26635,7 +26635,7 @@
         <v>1430</v>
       </c>
       <c r="E24" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -26689,7 +26689,7 @@
         <v>1430</v>
       </c>
       <c r="E27" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -26707,7 +26707,7 @@
         <v>1430</v>
       </c>
       <c r="E28" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -26743,7 +26743,7 @@
         <v>1430</v>
       </c>
       <c r="E30" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -26761,7 +26761,7 @@
         <v>1430</v>
       </c>
       <c r="E31" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -26799,7 +26799,7 @@
         <v>1430</v>
       </c>
       <c r="E33" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -26817,7 +26817,7 @@
         <v>1430</v>
       </c>
       <c r="E34" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -26875,7 +26875,7 @@
         <v>1430</v>
       </c>
       <c r="E37" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -26913,7 +26913,7 @@
         <v>1430</v>
       </c>
       <c r="E39" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -27029,7 +27029,7 @@
         <v>1430</v>
       </c>
       <c r="E45" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -27047,7 +27047,7 @@
         <v>1430</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -27065,7 +27065,7 @@
         <v>1430</v>
       </c>
       <c r="E47" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -27103,7 +27103,7 @@
         <v>1430</v>
       </c>
       <c r="E49" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -27121,7 +27121,7 @@
         <v>1430</v>
       </c>
       <c r="E50" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -27139,7 +27139,7 @@
         <v>1430</v>
       </c>
       <c r="E51" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -27257,7 +27257,7 @@
         <v>1430</v>
       </c>
       <c r="E57" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -27275,7 +27275,7 @@
         <v>1430</v>
       </c>
       <c r="E58" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -27411,7 +27411,7 @@
         <v>1430</v>
       </c>
       <c r="E65" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -27429,7 +27429,7 @@
         <v>1430</v>
       </c>
       <c r="E66" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -27505,7 +27505,7 @@
         <v>1430</v>
       </c>
       <c r="E70" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -27523,7 +27523,7 @@
         <v>1430</v>
       </c>
       <c r="E71" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -27541,7 +27541,7 @@
         <v>1430</v>
       </c>
       <c r="E72" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -27597,7 +27597,7 @@
         <v>1430</v>
       </c>
       <c r="E75" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -27615,7 +27615,7 @@
         <v>1430</v>
       </c>
       <c r="E76" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -27633,7 +27633,7 @@
         <v>1430</v>
       </c>
       <c r="E77" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -27691,7 +27691,7 @@
         <v>1430</v>
       </c>
       <c r="E80" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -27709,7 +27709,7 @@
         <v>1430</v>
       </c>
       <c r="E81" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -27727,7 +27727,7 @@
         <v>1430</v>
       </c>
       <c r="E82" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -27823,7 +27823,7 @@
         <v>1430</v>
       </c>
       <c r="E87" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -27841,7 +27841,7 @@
         <v>1430</v>
       </c>
       <c r="E88" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -27859,7 +27859,7 @@
         <v>1430</v>
       </c>
       <c r="E89" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -27877,7 +27877,7 @@
         <v>1430</v>
       </c>
       <c r="E90" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -27915,7 +27915,7 @@
         <v>1430</v>
       </c>
       <c r="E92" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -27953,7 +27953,7 @@
         <v>1430</v>
       </c>
       <c r="E94" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -28031,7 +28031,7 @@
         <v>1430</v>
       </c>
       <c r="E98" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -28149,7 +28149,7 @@
         <v>1430</v>
       </c>
       <c r="E104" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -28187,7 +28187,7 @@
         <v>1430</v>
       </c>
       <c r="E106" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -28325,7 +28325,7 @@
         <v>1430</v>
       </c>
       <c r="E113" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -28403,7 +28403,7 @@
         <v>1430</v>
       </c>
       <c r="E117" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -28421,7 +28421,7 @@
         <v>1430</v>
       </c>
       <c r="E118" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -28439,7 +28439,7 @@
         <v>1433</v>
       </c>
       <c r="E119" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -28448,7 +28448,7 @@
         <v>1275</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>1276</v>
@@ -28457,7 +28457,7 @@
         <v>1430</v>
       </c>
       <c r="E120" s="2">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -28466,7 +28466,7 @@
         <v>1282</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>1283</v>
@@ -28475,7 +28475,7 @@
         <v>1430</v>
       </c>
       <c r="E121" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -28484,7 +28484,7 @@
         <v>1288</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>1289</v>
@@ -28493,7 +28493,7 @@
         <v>1433</v>
       </c>
       <c r="E122" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -28502,7 +28502,7 @@
         <v>1292</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>1293</v>
@@ -28511,7 +28511,7 @@
         <v>1430</v>
       </c>
       <c r="E123" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -28520,7 +28520,7 @@
         <v>1297</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>1298</v>
@@ -28529,7 +28529,7 @@
         <v>1430</v>
       </c>
       <c r="E124" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -28538,7 +28538,7 @@
         <v>1305</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>1306</v>
@@ -28547,7 +28547,7 @@
         <v>1430</v>
       </c>
       <c r="E125" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -28556,7 +28556,7 @@
         <v>1311</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>1312</v>
@@ -28565,7 +28565,7 @@
         <v>1430</v>
       </c>
       <c r="E126" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -28574,7 +28574,7 @@
         <v>1317</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>1318</v>
@@ -28583,7 +28583,7 @@
         <v>1433</v>
       </c>
       <c r="E127" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -28592,7 +28592,7 @@
         <v>1323</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>1324</v>
@@ -28601,7 +28601,7 @@
         <v>1430</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -28610,7 +28610,7 @@
         <v>1329</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>1330</v>
@@ -28619,7 +28619,7 @@
         <v>1430</v>
       </c>
       <c r="E129" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -28628,7 +28628,7 @@
         <v>1335</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>1336</v>
@@ -28637,7 +28637,7 @@
         <v>1430</v>
       </c>
       <c r="E130" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -28646,7 +28646,7 @@
         <v>1341</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>1342</v>
@@ -28655,7 +28655,7 @@
         <v>1430</v>
       </c>
       <c r="E131" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -28664,7 +28664,7 @@
         <v>1347</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>1348</v>
@@ -28673,7 +28673,7 @@
         <v>1430</v>
       </c>
       <c r="E132" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -28682,7 +28682,7 @@
         <v>1353</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>1354</v>
@@ -28691,7 +28691,7 @@
         <v>1430</v>
       </c>
       <c r="E133" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -28700,7 +28700,7 @@
         <v>1359</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>1360</v>
@@ -28720,7 +28720,7 @@
         <v>1364</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>1365</v>
@@ -28740,7 +28740,7 @@
         <v>1368</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>1369</v>
@@ -28758,7 +28758,7 @@
         <v>1374</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>1375</v>
@@ -28767,7 +28767,7 @@
         <v>1430</v>
       </c>
       <c r="E137" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -28785,7 +28785,7 @@
         <v>1430</v>
       </c>
       <c r="E138" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -28803,7 +28803,7 @@
         <v>1430</v>
       </c>
       <c r="E139" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -28821,7 +28821,7 @@
         <v>1430</v>
       </c>
       <c r="E140" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -28839,7 +28839,7 @@
         <v>1430</v>
       </c>
       <c r="E141" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -28857,7 +28857,7 @@
         <v>1433</v>
       </c>
       <c r="E142" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -28875,7 +28875,7 @@
         <v>1430</v>
       </c>
       <c r="E143" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -28893,7 +28893,7 @@
         <v>1430</v>
       </c>
       <c r="E144" s="2">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F144" s="2"/>
     </row>
@@ -29028,7 +29028,7 @@
         <v>1288</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>1453</v>
@@ -29054,7 +29054,7 @@
         <v>719</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>1458</v>
@@ -29063,7 +29063,7 @@
         <v>1317</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1453</v>
@@ -29075,7 +29075,7 @@
         <v>1455</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29110,7 +29110,7 @@
         <v>1464</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -32062,10 +32062,10 @@
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -32085,10 +32085,10 @@
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C126" s="2">
         <v>3</v>
@@ -32108,10 +32108,10 @@
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C127" s="2">
         <v>4</v>
@@ -32131,10 +32131,10 @@
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C128" s="2">
         <v>4</v>
@@ -32154,10 +32154,10 @@
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C129" s="2">
         <v>2</v>
@@ -32177,10 +32177,10 @@
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -32200,10 +32200,10 @@
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -32223,10 +32223,10 @@
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C132" s="2">
         <v>2</v>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -168,7 +168,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-007 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-008 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-007 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-008 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -201,19 +201,19 @@
     <t>jira-export</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export, release-2.0 snapshot): Jira REST API v3 JSON of AQPI-32, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/EQE-MVP-Neeraj@demo/jira-export, release-2.0 snapshot): Jira REST API v3 JSON of AQPI-32, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44)</t>
+    <t>sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform-v2 (fe1ce44)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:27:15.652Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:57:50.867Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5566,7 +5566,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:17.630Z</t>
+    <t>2026-10-05T16:57:52.469Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5578,7 +5578,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:17.672Z</t>
+    <t>2026-10-05T16:57:52.512Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -26217,7 +26217,7 @@
         <v>1430</v>
       </c>
       <c r="E2" s="2">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -26335,7 +26335,7 @@
         <v>1430</v>
       </c>
       <c r="E8" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -26353,7 +26353,7 @@
         <v>1430</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -26371,7 +26371,7 @@
         <v>1430</v>
       </c>
       <c r="E10" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -26389,7 +26389,7 @@
         <v>1430</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -26407,7 +26407,7 @@
         <v>1430</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -26425,7 +26425,7 @@
         <v>1430</v>
       </c>
       <c r="E13" s="2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -26503,7 +26503,7 @@
         <v>1430</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -26521,7 +26521,7 @@
         <v>1430</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -26579,7 +26579,7 @@
         <v>1430</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -26617,7 +26617,7 @@
         <v>1430</v>
       </c>
       <c r="E23" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -26635,7 +26635,7 @@
         <v>1430</v>
       </c>
       <c r="E24" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -26653,7 +26653,7 @@
         <v>1430</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -26671,7 +26671,7 @@
         <v>1430</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -26689,7 +26689,7 @@
         <v>1430</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -26707,7 +26707,7 @@
         <v>1430</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -26725,7 +26725,7 @@
         <v>1430</v>
       </c>
       <c r="E29" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -26743,7 +26743,7 @@
         <v>1430</v>
       </c>
       <c r="E30" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -26761,7 +26761,7 @@
         <v>1430</v>
       </c>
       <c r="E31" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -26799,7 +26799,7 @@
         <v>1430</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -26817,7 +26817,7 @@
         <v>1430</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -26875,7 +26875,7 @@
         <v>1430</v>
       </c>
       <c r="E37" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -26913,7 +26913,7 @@
         <v>1430</v>
       </c>
       <c r="E39" s="2">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -26931,7 +26931,7 @@
         <v>1430</v>
       </c>
       <c r="E40" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -27029,7 +27029,7 @@
         <v>1430</v>
       </c>
       <c r="E45" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -27047,7 +27047,7 @@
         <v>1430</v>
       </c>
       <c r="E46" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -27065,7 +27065,7 @@
         <v>1430</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -27103,7 +27103,7 @@
         <v>1430</v>
       </c>
       <c r="E49" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -27121,7 +27121,7 @@
         <v>1430</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -27139,7 +27139,7 @@
         <v>1430</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -27257,7 +27257,7 @@
         <v>1430</v>
       </c>
       <c r="E57" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -27275,7 +27275,7 @@
         <v>1430</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -27313,7 +27313,7 @@
         <v>1430</v>
       </c>
       <c r="E60" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -27411,7 +27411,7 @@
         <v>1430</v>
       </c>
       <c r="E65" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -27429,7 +27429,7 @@
         <v>1430</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -27447,7 +27447,7 @@
         <v>1430</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -27505,7 +27505,7 @@
         <v>1430</v>
       </c>
       <c r="E70" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -27523,7 +27523,7 @@
         <v>1430</v>
       </c>
       <c r="E71" s="2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -27541,7 +27541,7 @@
         <v>1430</v>
       </c>
       <c r="E72" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -27579,7 +27579,7 @@
         <v>1430</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -27597,7 +27597,7 @@
         <v>1430</v>
       </c>
       <c r="E75" s="2">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -27615,7 +27615,7 @@
         <v>1430</v>
       </c>
       <c r="E76" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -27633,7 +27633,7 @@
         <v>1430</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -27691,7 +27691,7 @@
         <v>1430</v>
       </c>
       <c r="E80" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -27727,7 +27727,7 @@
         <v>1430</v>
       </c>
       <c r="E82" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -27823,7 +27823,7 @@
         <v>1430</v>
       </c>
       <c r="E87" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -27841,7 +27841,7 @@
         <v>1430</v>
       </c>
       <c r="E88" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -27859,7 +27859,7 @@
         <v>1430</v>
       </c>
       <c r="E89" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -27877,7 +27877,7 @@
         <v>1430</v>
       </c>
       <c r="E90" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -27915,7 +27915,7 @@
         <v>1430</v>
       </c>
       <c r="E92" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -27953,7 +27953,7 @@
         <v>1430</v>
       </c>
       <c r="E94" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -28031,7 +28031,7 @@
         <v>1430</v>
       </c>
       <c r="E98" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -28187,7 +28187,7 @@
         <v>1430</v>
       </c>
       <c r="E106" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -28325,7 +28325,7 @@
         <v>1430</v>
       </c>
       <c r="E113" s="2">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -28403,7 +28403,7 @@
         <v>1430</v>
       </c>
       <c r="E117" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -28421,7 +28421,7 @@
         <v>1430</v>
       </c>
       <c r="E118" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -28439,7 +28439,7 @@
         <v>1433</v>
       </c>
       <c r="E119" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -28457,7 +28457,7 @@
         <v>1430</v>
       </c>
       <c r="E120" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -28475,7 +28475,7 @@
         <v>1430</v>
       </c>
       <c r="E121" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -28493,7 +28493,7 @@
         <v>1433</v>
       </c>
       <c r="E122" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -28511,7 +28511,7 @@
         <v>1430</v>
       </c>
       <c r="E123" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -28529,7 +28529,7 @@
         <v>1430</v>
       </c>
       <c r="E124" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -28547,7 +28547,7 @@
         <v>1430</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -28565,7 +28565,7 @@
         <v>1430</v>
       </c>
       <c r="E126" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -28583,7 +28583,7 @@
         <v>1433</v>
       </c>
       <c r="E127" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -28601,7 +28601,7 @@
         <v>1430</v>
       </c>
       <c r="E128" s="2">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -28619,7 +28619,7 @@
         <v>1430</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -28673,7 +28673,7 @@
         <v>1430</v>
       </c>
       <c r="E132" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -28691,7 +28691,7 @@
         <v>1430</v>
       </c>
       <c r="E133" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -28749,7 +28749,7 @@
         <v>1430</v>
       </c>
       <c r="E136" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -28803,7 +28803,7 @@
         <v>1430</v>
       </c>
       <c r="E139" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -28821,7 +28821,7 @@
         <v>1430</v>
       </c>
       <c r="E140" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -28839,7 +28839,7 @@
         <v>1430</v>
       </c>
       <c r="E141" s="2">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -28857,7 +28857,7 @@
         <v>1433</v>
       </c>
       <c r="E142" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -28875,7 +28875,7 @@
         <v>1430</v>
       </c>
       <c r="E143" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -28893,7 +28893,7 @@
         <v>1430</v>
       </c>
       <c r="E144" s="2">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="F144" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -213,7 +213,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:57:50.867Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T17:10:55.049Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5566,7 +5566,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:57:52.469Z</t>
+    <t>2026-10-05T17:10:58.504Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5578,7 +5578,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-05T16:57:52.512Z</t>
+    <t>2026-10-05T17:10:58.549Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -26217,7 +26217,7 @@
         <v>1430</v>
       </c>
       <c r="E2" s="2">
-        <v>510</v>
+        <v>578</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -26335,7 +26335,7 @@
         <v>1430</v>
       </c>
       <c r="E8" s="2">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -26353,7 +26353,7 @@
         <v>1430</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -26371,7 +26371,7 @@
         <v>1430</v>
       </c>
       <c r="E10" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -26389,7 +26389,7 @@
         <v>1430</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -26407,7 +26407,7 @@
         <v>1430</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -26425,7 +26425,7 @@
         <v>1430</v>
       </c>
       <c r="E13" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -26579,7 +26579,7 @@
         <v>1430</v>
       </c>
       <c r="E21" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -26617,7 +26617,7 @@
         <v>1430</v>
       </c>
       <c r="E23" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -26635,7 +26635,7 @@
         <v>1430</v>
       </c>
       <c r="E24" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -26653,7 +26653,7 @@
         <v>1430</v>
       </c>
       <c r="E25" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -26671,7 +26671,7 @@
         <v>1430</v>
       </c>
       <c r="E26" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -26689,7 +26689,7 @@
         <v>1430</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -26707,7 +26707,7 @@
         <v>1430</v>
       </c>
       <c r="E28" s="2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -26725,7 +26725,7 @@
         <v>1430</v>
       </c>
       <c r="E29" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -26743,7 +26743,7 @@
         <v>1430</v>
       </c>
       <c r="E30" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -26761,7 +26761,7 @@
         <v>1430</v>
       </c>
       <c r="E31" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -26799,7 +26799,7 @@
         <v>1430</v>
       </c>
       <c r="E33" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -26817,7 +26817,7 @@
         <v>1430</v>
       </c>
       <c r="E34" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -26913,7 +26913,7 @@
         <v>1430</v>
       </c>
       <c r="E39" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -27029,7 +27029,7 @@
         <v>1430</v>
       </c>
       <c r="E45" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -27047,7 +27047,7 @@
         <v>1430</v>
       </c>
       <c r="E46" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -27065,7 +27065,7 @@
         <v>1430</v>
       </c>
       <c r="E47" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -27103,7 +27103,7 @@
         <v>1430</v>
       </c>
       <c r="E49" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -27121,7 +27121,7 @@
         <v>1430</v>
       </c>
       <c r="E50" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -27139,7 +27139,7 @@
         <v>1430</v>
       </c>
       <c r="E51" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -27257,7 +27257,7 @@
         <v>1430</v>
       </c>
       <c r="E57" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -27275,7 +27275,7 @@
         <v>1430</v>
       </c>
       <c r="E58" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -27313,7 +27313,7 @@
         <v>1430</v>
       </c>
       <c r="E60" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -27411,7 +27411,7 @@
         <v>1430</v>
       </c>
       <c r="E65" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -27429,7 +27429,7 @@
         <v>1430</v>
       </c>
       <c r="E66" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -27447,7 +27447,7 @@
         <v>1430</v>
       </c>
       <c r="E67" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -27505,7 +27505,7 @@
         <v>1430</v>
       </c>
       <c r="E70" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -27523,7 +27523,7 @@
         <v>1430</v>
       </c>
       <c r="E71" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -27541,7 +27541,7 @@
         <v>1430</v>
       </c>
       <c r="E72" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -27579,7 +27579,7 @@
         <v>1430</v>
       </c>
       <c r="E74" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -27597,7 +27597,7 @@
         <v>1430</v>
       </c>
       <c r="E75" s="2">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -27615,7 +27615,7 @@
         <v>1430</v>
       </c>
       <c r="E76" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -27691,7 +27691,7 @@
         <v>1430</v>
       </c>
       <c r="E80" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -27709,7 +27709,7 @@
         <v>1430</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -27727,7 +27727,7 @@
         <v>1430</v>
       </c>
       <c r="E82" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -27805,7 +27805,7 @@
         <v>1430</v>
       </c>
       <c r="E86" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -27823,7 +27823,7 @@
         <v>1430</v>
       </c>
       <c r="E87" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -27841,7 +27841,7 @@
         <v>1430</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -27859,7 +27859,7 @@
         <v>1430</v>
       </c>
       <c r="E89" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -27877,7 +27877,7 @@
         <v>1430</v>
       </c>
       <c r="E90" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -27915,7 +27915,7 @@
         <v>1430</v>
       </c>
       <c r="E92" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F92" s="2"/>
     </row>
@@ -27953,7 +27953,7 @@
         <v>1430</v>
       </c>
       <c r="E94" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -28031,7 +28031,7 @@
         <v>1430</v>
       </c>
       <c r="E98" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -28149,7 +28149,7 @@
         <v>1430</v>
       </c>
       <c r="E104" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -28187,7 +28187,7 @@
         <v>1430</v>
       </c>
       <c r="E106" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -28325,7 +28325,7 @@
         <v>1430</v>
       </c>
       <c r="E113" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -28403,7 +28403,7 @@
         <v>1430</v>
       </c>
       <c r="E117" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -28421,7 +28421,7 @@
         <v>1430</v>
       </c>
       <c r="E118" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -28439,7 +28439,7 @@
         <v>1433</v>
       </c>
       <c r="E119" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -28457,7 +28457,7 @@
         <v>1430</v>
       </c>
       <c r="E120" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -28475,7 +28475,7 @@
         <v>1430</v>
       </c>
       <c r="E121" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F121" s="2"/>
     </row>
@@ -28493,7 +28493,7 @@
         <v>1433</v>
       </c>
       <c r="E122" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -28511,7 +28511,7 @@
         <v>1430</v>
       </c>
       <c r="E123" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -28583,7 +28583,7 @@
         <v>1433</v>
       </c>
       <c r="E127" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -28601,7 +28601,7 @@
         <v>1430</v>
       </c>
       <c r="E128" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -28619,7 +28619,7 @@
         <v>1430</v>
       </c>
       <c r="E129" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -28637,7 +28637,7 @@
         <v>1430</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -28673,7 +28673,7 @@
         <v>1430</v>
       </c>
       <c r="E132" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -28749,7 +28749,7 @@
         <v>1430</v>
       </c>
       <c r="E136" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -28767,7 +28767,7 @@
         <v>1430</v>
       </c>
       <c r="E137" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -28785,7 +28785,7 @@
         <v>1430</v>
       </c>
       <c r="E138" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -28821,7 +28821,7 @@
         <v>1430</v>
       </c>
       <c r="E140" s="2">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -28839,7 +28839,7 @@
         <v>1430</v>
       </c>
       <c r="E141" s="2">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -28857,7 +28857,7 @@
         <v>1433</v>
       </c>
       <c r="E142" s="2">
-        <v>378</v>
+        <v>341</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -28875,7 +28875,7 @@
         <v>1430</v>
       </c>
       <c r="E143" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -28893,7 +28893,7 @@
         <v>1430</v>
       </c>
       <c r="E144" s="2">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="F144" s="2"/>
     </row>
